--- a/agriculture 35.xlsx
+++ b/agriculture 35.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate of Area, Production and Productivity of Coconut in Kerala</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -79,7 +76,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -101,14 +98,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -170,7 +159,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -199,165 +188,165 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.11"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="4" t="n">
+        <v>-2.76597792334202</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-2.39017000504965</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.38690064944038</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-2.76597792334202</v>
+        <v>1.31364309501079</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-2.39017000504965</v>
+        <v>2.10381100189687</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.38690064944038</v>
+        <v>0.784583620096346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1.31364309501079</v>
+        <v>-1.8291046649527</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2.10381100189687</v>
+        <v>0.439115014355673</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.784583620096346</v>
+        <v>2.30811253755805</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-1.8291046649527</v>
+        <v>-0.457639672686228</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.439115014355673</v>
+        <v>-1.24432486968219</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.30811253755805</v>
+        <v>-0.787611800827659</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-0.457639672686228</v>
+        <v>-1.10437180390852</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.24432486968219</v>
+        <v>-8.32623871956411</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.787611800827659</v>
+        <v>-7.30624327233584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>-1.10437180390852</v>
+        <v>-2.69393573351623</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-8.32623871956411</v>
+        <v>-2.86032689450223</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-7.30624327233584</v>
+        <v>-0.159674843954127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>-2.69393573351623</v>
+        <v>0.0662771568677778</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.86032689450223</v>
+        <v>1.31931166347992</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.159674843954127</v>
+        <v>1.25036347775516</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0.0662771568677778</v>
+        <v>-0.0224719987068744</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.31931166347992</v>
+        <v>-9.1526703151538</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.25036347775516</v>
+        <v>-9.13268236645606</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-0.0224719987068744</v>
+        <v>1.05589555927106</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-9.1526703151538</v>
+        <v>-0.540091400083087</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-9.13268236645606</v>
+        <v>-1.5802781289507</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>1.05589555927106</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-0.540091400083087</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-1.5802781289507</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 35.xlsx
+++ b/agriculture 35.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">2020-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics, Coconut Development Board Statistics</t>
@@ -76,7 +79,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -106,6 +109,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -150,7 +159,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -168,6 +177,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,13 +354,28 @@
         <v>-1.5802781289507</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/agriculture 35.xlsx
+++ b/agriculture 35.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics, Coconut Development Board Statistics</t>
@@ -79,7 +79,7 @@
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -109,12 +109,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -180,7 +174,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/agriculture 35.xlsx
+++ b/agriculture 35.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics, Coconut Development Board Statistics</t>
